--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T12:53:52+00:00</t>
+    <t>2026-02-25T15:06:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T15:06:56+00:00</t>
+    <t>2026-02-25T15:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T15:46:18+00:00</t>
+    <t>2026-02-26T09:19:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T09:19:47+00:00</t>
+    <t>2026-02-26T10:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:12:23+00:00</t>
+    <t>2026-02-27T08:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T08:04:50+00:00</t>
+    <t>2026-02-27T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T13:41:32+00:00</t>
+    <t>2026-02-27T14:50:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T14:50:48+00:00</t>
+    <t>2026-02-27T15:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T15:19:26+00:00</t>
+    <t>2026-03-02T08:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T08:02:27+00:00</t>
+    <t>2026-03-02T11:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T11:53:36+00:00</t>
+    <t>2026-03-03T10:14:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T10:14:52+00:00</t>
+    <t>2026-03-03T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T12:03:19+00:00</t>
+    <t>2026-03-03T13:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T13:32:32+00:00</t>
+    <t>2026-03-03T14:15:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:15:20+00:00</t>
+    <t>2026-03-03T14:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:31:56+00:00</t>
+    <t>2026-03-03T15:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T15:16:40+00:00</t>
+    <t>2026-03-03T15:50:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T15:50:01+00:00</t>
+    <t>2026-03-03T23:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T23:41:56+00:00</t>
+    <t>2026-03-04T10:28:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T10:28:14+00:00</t>
+    <t>2026-03-04T10:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T10:52:48+00:00</t>
+    <t>2026-03-04T11:52:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T11:52:29+00:00</t>
+    <t>2026-03-04T12:46:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T12:46:59+00:00</t>
+    <t>2026-03-04T13:04:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T13:04:58+00:00</t>
+    <t>2026-03-04T13:16:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T13:16:06+00:00</t>
+    <t>2026-03-04T14:00:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:00:20+00:00</t>
+    <t>2026-03-04T14:06:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:06:40+00:00</t>
+    <t>2026-03-04T14:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:16:37+00:00</t>
+    <t>2026-03-04T14:27:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-identifier-iknr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:27:48+00:00</t>
+    <t>2026-03-06T10:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
